--- a/pc/public/import_template/base/background_task.xlsx
+++ b/pc/public/import_template/base/background_task.xlsx
@@ -45,10 +45,10 @@
     <t xml:space="preserve">&lt;%=comment.err_msg%&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;%=comment.begin_time%&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;%=comment.end_time%&gt;</t>
+    <t xml:space="preserve">&lt;%=comment.begin_time_lbl%&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;%=comment.end_time_lbl%&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;%=comment.rem%&gt;</t>
